--- a/JsonConverter/ExcelFiles/OO_Stage3CueSheet.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Stage3CueSheet.xlsx
@@ -1,20 +1,20 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OO_Stage3CueSheet" sheetId="1" state="visible" r:id="rId1"/>
-  </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties">
+  <Application>Microsoft Excel Compatible / Openpyxl 3.1.5</Application>
+  <AppVersion>3.1</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties">
+  <dc:creator xmlns:dc="http://purl.org/dc/elements/1.1/">openpyxl</dc:creator>
+  <dcterms:created xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xsi:type="dcterms:W3CDTF">2026-06-06T05:35:44Z</dcterms:created>
+  <dcterms:modified xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xsi:type="dcterms:W3CDTF">2026-06-06T06:03:01Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="3">
@@ -143,7 +143,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -426,13 +426,28 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OO_Stage3CueSheet" sheetId="1" state="visible" r:id="rId1"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF4"/>
+  <dimension ref="A1:AG4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,100 +513,105 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>클리어 대사 ID</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>??? ID</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>?? ?? ID</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>?? ???? ID</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>? ?? ID</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>? ?? ID</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>?? ?? ID</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>?? ??? ID</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>?? ?? ??? ID</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>?? ?? ??? ID</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>?? ??? ID</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>??? ?? ID ??(| ??)</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>??? ?? ?? ??(| ??)</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>?? ?? ??</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>?? ?? ?? ?? ??</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>?? ?? ?? ?? ??</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>?? ?? ??</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>?? ????? ??</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>?? ????? ??</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Encounter ?? ??</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>?? ?? ??</t>
         </is>
@@ -725,35 +745,40 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
           <t>float</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -822,100 +847,105 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>ClearDialogueId</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>StageQuestId</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>JulguToolId</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>JulguTutorialId</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>KoreanCakeItemId</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>HoneyIngredientId</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>HoneyKoreanCakeItemId</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>CakeOnlyChoiceId</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>MakeHoneyCakeChoiceId</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>GiveHoneyCakeChoiceId</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>DeathRetryChoiceId</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>ClearRewardItemIds</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>ClearRewardCounts</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>NextRoadGroupName</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>SangunStartScaleRatio</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>SangunThreateningScaleRatio</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>SangunAppearSeconds</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>ThreateningAnimationSpeed</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>AttackingAnimationSpeed</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>EncounterWaitSeconds</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>DeathMessage</t>
         </is>
@@ -984,88 +1014,93 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
+          <t>character_Sangun_04</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>Stage3__Quest_01</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>Julgu</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>narration_tutorial_14</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>OO_KoreanCake_1</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>Ing_Honey_01</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>OO_HoneyKoreanCake_1</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>Choice_Stage3_SungunQuest_02</t>
         </is>
       </c>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>Choice_Stage3_SungunQuest_01</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Choice_Stage3_SungunQuest_03</t>
         </is>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="W4" s="2" t="inlineStr">
         <is>
           <t>Choice_Stage3_SungunQuest_04</t>
         </is>
       </c>
-      <c r="W4" s="2" t="inlineStr">
+      <c r="X4" s="2" t="inlineStr">
         <is>
           <t>Ing_Carrot_01</t>
         </is>
       </c>
-      <c r="X4" s="2" t="inlineStr">
+      <c r="Y4" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Y4" s="2" t="inlineStr">
+      <c r="Z4" s="2" t="inlineStr">
         <is>
           <t>4th_Road_to_Stage4</t>
         </is>
       </c>
-      <c r="Z4" s="2" t="n">
+      <c r="AA4" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="AA4" s="2" t="n">
+      <c r="AB4" s="2" t="n">
         <v>0.7</v>
       </c>
-      <c r="AB4" s="2" t="n">
+      <c r="AC4" s="2" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AC4" s="2" t="n">
-        <v>0.7</v>
       </c>
       <c r="AD4" s="2" t="n">
         <v>0.7</v>
       </c>
       <c r="AE4" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AF4" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AF4" s="2" t="inlineStr">
+      <c r="AG4" s="2" t="inlineStr">
         <is>
           <t>YOU DIE</t>
         </is>

--- a/JsonConverter/ExcelFiles/OO_Stage3CueSheet.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Stage3CueSheet.xlsx
@@ -1,20 +1,20 @@
 
-<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties">
-  <Application>Microsoft Excel Compatible / Openpyxl 3.1.5</Application>
-  <AppVersion>3.1</AppVersion>
-</Properties>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OO_Stage3CueSheet" sheetId="1" state="visible" r:id="rId1"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
 </file>
 
-<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
-<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties">
-  <dc:creator xmlns:dc="http://purl.org/dc/elements/1.1/">openpyxl</dc:creator>
-  <dcterms:created xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xsi:type="dcterms:W3CDTF">2026-06-06T05:35:44Z</dcterms:created>
-  <dcterms:modified xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xsi:type="dcterms:W3CDTF">2026-06-06T06:03:01Z</dcterms:modified>
-</cp:coreProperties>
-</file>
-
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="3">
@@ -143,7 +143,7 @@
 </styleSheet>
 </file>
 
-<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -426,28 +426,13 @@
 </a:theme>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OO_Stage3CueSheet" sheetId="1" state="visible" r:id="rId1"/>
-  </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG4"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,150 +453,160 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Road 임무 데이터 ID</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Road 임무 fallback 문장</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>???? ?? ID</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>???? ?? ID</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>MFC ?? ID</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>?? ?? ID</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>EntryPoint A ID</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>?? ? ?? ID</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>???? ?? ?? ID</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>???? ?? ?? ID</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>???? ?? ??? ?? ID</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>클리어 대사 ID</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>??? ID</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>?? ?? ID</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>?? ???? ID</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>? ?? ID</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>? ?? ID</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>?? ?? ID</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>?? ??? ID</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>?? ?? ??? ID</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>?? ?? ??? ID</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>?? ??? ID</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>??? ?? ID ??(| ??)</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>??? ?? ?? ??(| ??)</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>?? ?? ??</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>?? ?? ?? ?? ??</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>?? ?? ?? ?? ??</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>?? ?? ??</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>?? ????? ??</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>?? ????? ??</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Encounter ?? ??</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>?? ?? ??</t>
         </is>
@@ -750,35 +745,45 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>float</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -802,150 +807,160 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>RoadMissionDataId</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RoadMissionFallbackText</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>StageGroupId</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>EncounterGroupId</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>MFCRoleId</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>SangunRoleId</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>EntryPointAId</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>SangunFirstDialogueId</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>EncounterSangunDialogueId</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>EncounterMoranDialogueId</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>EncounterQuestDialogueId</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>ClearDialogueId</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>StageQuestId</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>JulguToolId</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>JulguTutorialId</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>KoreanCakeItemId</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>HoneyIngredientId</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>HoneyKoreanCakeItemId</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>CakeOnlyChoiceId</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>MakeHoneyCakeChoiceId</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>GiveHoneyCakeChoiceId</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>DeathRetryChoiceId</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>ClearRewardItemIds</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>ClearRewardCounts</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>NextRoadGroupName</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>SangunStartScaleRatio</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>SangunThreateningScaleRatio</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>SangunAppearSeconds</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>ThreateningAnimationSpeed</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>AttackingAnimationSpeed</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>EncounterWaitSeconds</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>DeathMessage</t>
         </is>
@@ -969,138 +984,148 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>Stage3_Road_Quest_01</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>남쪽 숲으로 가세요!</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>Stage3Group</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>EncounterGroup</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>MFC</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Sangun</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>EntryPoint_A</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>character_Sangun_01</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>character_Sangun_02</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>character_Moran_08</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>character_Sangun_03</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>character_Sangun_04</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>Stage3__Quest_01</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>Julgu</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>narration_tutorial_14</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>OO_KoreanCake_1</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>Ing_Honey_01</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>OO_HoneyKoreanCake_1</t>
         </is>
       </c>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>Choice_Stage3_SungunQuest_02</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="W4" s="2" t="inlineStr">
         <is>
           <t>Choice_Stage3_SungunQuest_01</t>
         </is>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="X4" s="2" t="inlineStr">
         <is>
           <t>Choice_Stage3_SungunQuest_03</t>
         </is>
       </c>
-      <c r="W4" s="2" t="inlineStr">
+      <c r="Y4" s="2" t="inlineStr">
         <is>
           <t>Choice_Stage3_SungunQuest_04</t>
         </is>
       </c>
-      <c r="X4" s="2" t="inlineStr">
+      <c r="Z4" s="2" t="inlineStr">
         <is>
           <t>Ing_Carrot_01</t>
         </is>
       </c>
-      <c r="Y4" s="2" t="inlineStr">
+      <c r="AA4" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Z4" s="2" t="inlineStr">
+      <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>4th_Road_to_Stage4</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="n">
+      <c r="AC4" s="2" t="n">
         <v>0.5</v>
-      </c>
-      <c r="AB4" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AC4" s="2" t="n">
-        <v>1.2</v>
       </c>
       <c r="AD4" s="2" t="n">
         <v>0.7</v>
       </c>
       <c r="AE4" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF4" s="2" t="n">
         <v>0.7</v>
       </c>
-      <c r="AF4" s="2" t="n">
+      <c r="AG4" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AH4" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AG4" s="2" t="inlineStr">
+      <c r="AI4" s="2" t="inlineStr">
         <is>
           <t>YOU DIE</t>
         </is>
